--- a/One-Abbott平台Phase1_任务计划.xlsx
+++ b/One-Abbott平台Phase1_任务计划.xlsx
@@ -87,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -109,11 +109,44 @@
         <color rgb="00B7C3D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C3D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C3D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C3D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B7C3D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,12 +170,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2359,7 +2396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2463,12 +2500,12 @@
           <t>F01-1-1</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>模块1·微前端平台底座</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Portal Shell 宿主</t>
         </is>
@@ -2507,7 +2544,9 @@
       <c r="M3" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="10" t="n">
+        <v>30.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2515,8 +2554,8 @@
           <t>F01-1-2</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SSO 会话与权限 SDK</t>
@@ -2551,7 +2590,7 @@
       <c r="M4" s="6" t="n">
         <v>6.75</v>
       </c>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2559,8 +2598,8 @@
           <t>F01-1-3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Design Tokens 与主题</t>
@@ -2595,7 +2634,7 @@
       <c r="M5" s="6" t="n">
         <v>3.75</v>
       </c>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2603,8 +2642,8 @@
           <t>F01-1-4</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>MF 注册表与运行时加载</t>
@@ -2639,7 +2678,7 @@
       <c r="M6" s="6" t="n">
         <v>7.75</v>
       </c>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2647,8 +2686,8 @@
           <t>F01-1-5</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="12" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>错误兜底与事件总线</t>
@@ -2683,227 +2722,360 @@
       <c r="M7" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="N8" s="9" t="n">
-        <v>30.25</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>F01-2-1</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>MF 工程化</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>模块脚手架模板</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>CLI 模板/目录规范/Mock/本地联调</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>F01-2-1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MF 工程化</t>
-        </is>
-      </c>
+          <t>F01-2-2</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>模块脚手架模板</t>
+          <t>shared 共享包治理</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>CLI 模板/目录规范/Mock/本地联调</t>
+          <t>白名单/单例版本/singleton 协商/CI 校验</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L9" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N9" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="N9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>F01-2-2</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
+          <t>F01-3-1</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>组件库</t>
+        </is>
+      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>shared 共享包治理</t>
+          <t>基础组件</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>白名单/单例版本/singleton 协商/CI 校验</t>
+          <t>Antd 定制/主题接入/表单表格封装</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>F01-3-2</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>业务组件</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>内容卡片/审核流/签到大屏等 8~10 个</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="N11" s="9" t="n">
-        <v>9.75</v>
-      </c>
+      <c r="L11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>F01-3-1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>组件库</t>
+          <t>F01-4-1</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>契约与 CI</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>基础组件</t>
+          <t>contracts 契约包</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Antd 定制/主题接入/表单表格封装</t>
+          <t>DTO/事件/权限码定义/发布 registry</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N12" s="4" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>F01-3-2</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
+          <t>F01-4-2</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>业务组件</t>
+          <t>模块流水线与发布</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>内容卡片/审核流/签到大屏等 8~10 个</t>
+          <t>流水线模板/CDN 发布/manifest PR/回滚脚本</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>F02-1-1</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>模块2·统一身份与SSO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>SSO 集成</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Entra ID OIDC 对接</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>应用注册/回调/Token 校验/MFA 预留</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="N14" s="9" t="n">
-        <v>19</v>
+      <c r="H14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>F01-4-1</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>契约与 CI</t>
-        </is>
-      </c>
+          <t>F02-1-2</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>contracts 契约包</t>
+          <t>登录/登出/会话</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>DTO/事件/权限码定义/发布 registry</t>
+          <t>统一登录页/单点登出/会话超时刷新</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -2916,371 +3088,616 @@
         <v>0.5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="M15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="4" t="n"/>
+        <v>5.5</v>
+      </c>
+      <c r="N15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>F01-4-2</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
+          <t>F02-2-1</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>用户与组织</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>模块流水线与发布</t>
+          <t>用户/角色/组织管理</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>流水线模板/CDN 发布/manifest PR/回滚脚本</t>
+          <t>用户台账/组织树/角色授权界面</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>F02-3-1</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>权限模型</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>RBAC+数据范围</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>权限码/组织区域数据范围/菜单接口</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="N16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="N17" s="9" t="n">
-        <v>11.25</v>
+      <c r="H17" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>F02-1-1</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>模块2·统一身份与SSO</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>SSO 集成</t>
+          <t>F02-4-1</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>审计</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Entra ID OIDC 对接</t>
+          <t>登录与权限审计</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>应用注册/回调/Token 校验/MFA 预留</t>
+          <t>审计事件接入统一审计服务/查询</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G18" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="J18" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" s="4" t="n"/>
+        <v>2.75</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>F02-1-2</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
+          <t>F03-1-1</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>模块3·后端通用服务</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>通知服务</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>登录/登出/会话</t>
+          <t>渠道封装与模板</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>统一登录页/单点登出/会话超时刷新</t>
+          <t>企微/邮件/短信适配/模板变量/发送记录</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K19" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N19" s="4" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="20">
-      <c r="N20" s="9" t="n">
-        <v>12</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>F03-2-1</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>工作流服务</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>审批流引擎</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>状态机/审批任务/回调/超时代理</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>F02-2-1</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>用户与组织</t>
+          <t>F03-3-1</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>规则服务</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>用户/角色/组织管理</t>
+          <t>业务规则引擎</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>用户台账/组织树/角色授权界面</t>
+          <t>表达式解析/规则版本/热更新/试用接口</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="K21" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>F03-4-1</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>文件服务</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>上传下载</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>SAS 签名/类型校验/病毒扫描钩子</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="N22" s="9" t="n">
-        <v>10.5</v>
+      <c r="K22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>F02-3-1</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>权限模型</t>
+          <t>F03-5-1</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>审计服务</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>RBAC+数据范围</t>
+          <t>统一操作审计</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>权限码/组织区域数据范围/菜单接口</t>
+          <t>采集中间件/WORM 归档/查询接口</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K23" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>F03-6-1</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>事件骨干</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Service Bus 主题订阅</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>命名规范/CloudEvents/Outbox/幂等/DLQ</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="N24" s="9" t="n">
-        <v>7.5</v>
+      <c r="K24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>F02-4-1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>审计</t>
+          <t>F03-7-1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>API 网关</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>登录与权限审计</t>
+          <t>内部 APIM 治理</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>审计事件接入统一审计服务/查询</t>
+          <t>API 产品/订阅/限流/JWT 策略/Dev Portal</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N25" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
-      <c r="N26" s="9" t="n">
-        <v>2.75</v>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>F03-8-1</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>服务模板</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>后端脚手架</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>.NET 模板/鉴权库/审计中间件/错误规范</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>F03-1-1</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>模块3·后端通用服务</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>通知服务</t>
+          <t>F04-1-1</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>模块4·内容能力中心</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>产品中心</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>渠道封装与模板</t>
+          <t>产品模型与列表</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>企微/邮件/短信适配/模板变量/发送记录</t>
+          <t>产品档案模型/列表筛选/分页</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>1</v>
@@ -3289,157 +3706,276 @@
         <v>0.5</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N27" s="4" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="28">
-      <c r="N28" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>F04-1-2</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>产品详情</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>详情聚合/适应症规格资料/多语言预留</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>F03-2-1</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>工作流服务</t>
-        </is>
-      </c>
+          <t>F04-1-3</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="12" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>审批流引擎</t>
+          <t>资料下载/试剂速查</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>状态机/审批任务/回调/超时代理</t>
+          <t>附件管理/关键词速查接口</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K29" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>F04-2-1</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>学术中心</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>文献库</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>文献元数据/分类标签/附件/列表</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" s="6" t="n">
+      <c r="L30" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="N29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="N30" s="9" t="n">
-        <v>6.5</v>
+      <c r="N30" s="10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>F03-3-1</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>规则服务</t>
-        </is>
-      </c>
+          <t>F04-2-2</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>业务规则引擎</t>
+          <t>培训课程</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>表达式解析/规则版本/热更新/试用接口</t>
+          <t>课程章节/学习记录简版</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>F04-3-1</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>内容治理</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>内容审核发布</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>提交→审核→发布状态机/版本/下线</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="H32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="N32" s="9" t="n">
-        <v>4.5</v>
+      <c r="J32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>F03-4-1</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>文件服务</t>
-        </is>
-      </c>
+          <t>F04-3-2</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="12" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>上传下载</t>
+          <t>内容搜索（基础）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>SAS 签名/类型校验/病毒扫描钩子</t>
+          <t>全文索引/筛选排序（AI Search 后置）</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0.5</v>
@@ -3450,86 +3986,176 @@
       <c r="M33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="12" t="n"/>
     </row>
     <row r="34">
-      <c r="N34" s="9" t="n">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>F04-4-1</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Content MF</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>产品 MF 页面</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>产品列表/详情/资料下载页面</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="6" t="n">
         <v>4</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N34" s="10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>F03-5-1</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>审计服务</t>
-        </is>
-      </c>
+          <t>F04-4-2</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>统一操作审计</t>
+          <t>学术 MF 页面</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>采集中间件/WORM 归档/查询接口</t>
+          <t>文献/课程列表详情/搜索页</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N35" s="4" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="N35" s="12" t="n"/>
     </row>
     <row r="36">
-      <c r="N36" s="9" t="n">
-        <v>4</v>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>F05-1-1</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>模块5·会议能力中心</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>会议管理</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>会议/议程管理</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>会议创建/议程讲者/材料管理</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>F03-6-1</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>事件骨干</t>
+          <t>F05-2-1</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>报名签到</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Service Bus 主题订阅</t>
+          <t>报名与审核</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>命名规范/CloudEvents/Outbox/幂等/DLQ</t>
+          <t>报名表单/名额控制/审核流</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
@@ -3542,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>1</v>
@@ -3554,35 +4180,76 @@
         <v>0.5</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" s="4" t="n"/>
+        <v>5.5</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>10.25</v>
+      </c>
     </row>
     <row r="38">
-      <c r="N38" s="9" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>F05-2-2</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>二维码签到</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>二维码生成/核销/签到统计</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>F03-7-1</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>API 网关</t>
+          <t>F05-3-1</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>直播对接（最简）</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>内部 APIM 治理</t>
+          <t>第三方直播对接</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>API 产品/订阅/限流/JWT 策略/Dev Portal</t>
+          <t>预约/跳转/回放链接管理</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3595,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0.5</v>
@@ -3607,143 +4274,243 @@
         <v>0.25</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" s="4" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
-      <c r="N40" s="9" t="n">
-        <v>4</v>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>F05-4-1</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Event MF</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>会议 MF 页面</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>会议列表/详情/报名/签到页</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N40" s="10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>F03-8-1</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr"/>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>服务模板</t>
+          <t>F06-1-1</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>模块6·客户数据能力中心</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>主数据管理</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>后端脚手架</t>
+          <t>HCP/HCO 主数据</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>.NET 模板/鉴权库/审计中间件/错误规范</t>
+          <t>档案 CRUD/批量导入/查重合并基础</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>F06-2-1</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>客户360</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>C360 聚合视图</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>档案+会议+浏览+标签聚合接口/缓存</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="J41" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M41" s="6" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="N42" s="9" t="n">
-        <v>4.25</v>
+      <c r="K42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N42" s="10" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>F04-1-1</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>模块4·内容能力中心</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>产品中心</t>
+          <t>F06-3-1</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>标签（简版）</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>产品模型与列表</t>
+          <t>规则标签</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>产品档案模型/列表筛选/分页</t>
+          <t>标签定义/规则打标/标签查询</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N43" s="4" t="n"/>
+        <v>3.5</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>F04-1-2</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr"/>
-      <c r="C44" s="4" t="inlineStr"/>
+          <t>F06-4-1</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Customer MF</t>
+        </is>
+      </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>产品详情</t>
+          <t>客户 MF 页面</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>详情聚合/适应症规格资料/多语言预留</t>
+          <t>HCP 列表详情/C360 视图页</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
@@ -3752,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>1</v>
@@ -3761,1191 +4528,387 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N44" s="4" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>F04-1-3</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr"/>
+          <t>F07-1-1</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>模块7·平台工程</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>环境与基建</t>
+        </is>
+      </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>资料下载/试剂速查</t>
+          <t>AKS 三环境 + IaC</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>附件管理/关键词速查接口</t>
+          <t>Terraform 模块/网络/私有集群</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>F07-2-1</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>CI/CD</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>流水线与质量门禁</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>构建/Trivy/sonar/部署/冒烟门禁</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I46" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M45" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="N46" s="9" t="n">
-        <v>18.5</v>
+      <c r="J46" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>F04-2-1</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>学术中心</t>
+          <t>F07-3-1</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>可观测</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>文献库</t>
+          <t>日志监控告警</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>文献元数据/分类标签/附件/列表</t>
+          <t>App Insights/日志/告警规则/大盘</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N47" s="4" t="n"/>
+        <v>3.25</v>
+      </c>
+      <c r="N47" s="10" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>F04-2-2</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="4" t="inlineStr"/>
+          <t>F08-1-1</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>模块8·非功能与交付</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>性能与安全</t>
+        </is>
+      </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>培训课程</t>
+          <t>压测与安全基线</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>课程章节/学习记录简版</t>
+          <t>核心接口压测/依赖扫描清零/权限用例</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K48" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N48" s="10" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>F08-2-1</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>UAT 与上线</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>UAT 与上线值守</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>UAT 组织/缺陷修复/上线预演/值守</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="N49" s="9" t="n">
-        <v>13</v>
+      <c r="G49" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N49" s="10" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>F04-3-1</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>内容治理</t>
+          <t>F08-3-1</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>文档与交接</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>内容审核发布</t>
+          <t>架构/接口/用户文档</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>提交→审核→发布状态机/版本/下线</t>
+          <t>架构文档/接口手册/运维交接/培训</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N50" s="4" t="n"/>
+        <v>7.75</v>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>F04-3-2</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>内容搜索（基础）</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>全文索引/筛选排序（AI Search 后置）</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M51" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="N52" s="9" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>F04-4-1</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr"/>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Content MF</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>产品 MF 页面</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>产品列表/详情/资料下载页面</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>F04-4-2</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>学术 MF 页面</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>文献/课程列表详情/搜索页</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="N55" s="9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>F05-1-1</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>模块5·会议能力中心</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>会议管理</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>会议/议程管理</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>会议创建/议程讲者/材料管理</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="N57" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>F05-2-1</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>报名签到</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>报名与审核</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>报名表单/名额控制/审核流</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M58" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>F05-2-2</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>二维码签到</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>二维码生成/核销/签到统计</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M59" s="6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="N60" s="9" t="n">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>F05-3-1</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr"/>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>直播对接（最简）</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>第三方直播对接</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>预约/跳转/回放链接管理</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="N62" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>F05-4-1</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr"/>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Event MF</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>会议 MF 页面</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>会议列表/详情/报名/签到页</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M63" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="N63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="N64" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>F06-1-1</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>模块6·客户数据能力中心</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>主数据管理</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>HCP/HCO 主数据</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>档案 CRUD/批量导入/查重合并基础</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="N66" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>F06-2-1</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr"/>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>客户360</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>C360 聚合视图</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>档案+会议+浏览+标签聚合接口/缓存</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M67" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="N68" s="9" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>F06-3-1</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr"/>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>标签（简版）</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>规则标签</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>标签定义/规则打标/标签查询</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L69" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M69" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="N70" s="9" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>F06-4-1</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Customer MF</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>客户 MF 页面</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>HCP 列表详情/C360 视图页</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M71" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N71" s="4" t="n"/>
-    </row>
-    <row r="72">
-      <c r="N72" s="9" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>F07-1-1</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>模块7·平台工程</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>环境与基建</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>AKS 三环境 + IaC</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Terraform 模块/网络/私有集群</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K73" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L73" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M73" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="N74" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>F07-2-1</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>CI/CD</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>流水线与质量门禁</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>构建/Trivy/sonar/部署/冒烟门禁</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L75" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N75" s="4" t="n"/>
-    </row>
-    <row r="76">
-      <c r="N76" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>F07-3-1</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>可观测</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>日志监控告警</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>App Insights/日志/告警规则/大盘</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M77" s="6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N77" s="4" t="n"/>
-    </row>
-    <row r="78">
-      <c r="N78" s="9" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>F08-1-1</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>模块8·非功能与交付</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>性能与安全</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>压测与安全基线</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>核心接口压测/依赖扫描清零/权限用例</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I79" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K79" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L79" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M79" s="6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N79" s="4" t="n"/>
-    </row>
-    <row r="80">
-      <c r="N80" s="9" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>F08-2-1</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr"/>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>UAT 与上线</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>UAT 与上线值守</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>UAT 组织/缺陷修复/上线预演/值守</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L81" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N81" s="4" t="n"/>
-    </row>
-    <row r="82">
-      <c r="N82" s="9" t="n">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>F08-3-1</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr"/>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>文档与交接</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>架构/接口/用户文档</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>架构文档/接口手册/运维交接/培训</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L83" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M83" s="6" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="N83" s="4" t="n"/>
-    </row>
-    <row r="84">
-      <c r="N84" s="9" t="n">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr"/>
-      <c r="C85" s="7" t="inlineStr"/>
-      <c r="D85" s="7" t="inlineStr"/>
-      <c r="E85" s="7" t="inlineStr"/>
-      <c r="F85" s="8" t="n">
+      <c r="B51" s="7" t="inlineStr"/>
+      <c r="C51" s="7" t="inlineStr"/>
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr"/>
+      <c r="F51" s="8" t="n">
         <v>15.25</v>
       </c>
-      <c r="G85" s="8" t="n">
+      <c r="G51" s="8" t="n">
         <v>70.5</v>
       </c>
-      <c r="H85" s="8" t="n">
+      <c r="H51" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="I85" s="8" t="n">
+      <c r="I51" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="J85" s="8" t="n">
+      <c r="J51" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="K85" s="8" t="n">
+      <c r="K51" s="8" t="n">
         <v>37.25</v>
       </c>
-      <c r="L85" s="8" t="n">
+      <c r="L51" s="8" t="n">
         <v>26.25</v>
       </c>
-      <c r="M85" s="8" t="n">
+      <c r="M51" s="8" t="n">
         <v>281.75</v>
       </c>
-      <c r="N85" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="29">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="N32:N33"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="N37:N38"/>
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="N27:N29"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="N3:N7"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B3:B13"/>
+    <mergeCell ref="B27:B35"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="C14:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5283,3258 +5246,3258 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>一、需求与设计（W1~W3）</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Mandy/Wade/DevB</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>2027/01/04</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>需求澄清与 SRS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>2027/01/04</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>2027/01/15</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>AI 辅助起草</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr"/>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr"/>
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L4" s="13" t="n">
+      <c r="L4" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>业务场景与功能清单确认（6 大模块）</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>2027/01/04</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>AI 生成问卷/纪要</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr"/>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L5" s="15" t="n">
+      <c r="L5" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>原型与用户故事（Portal/三域 MF）</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>2027/01/06</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>2027/01/15</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>AI 生成原型稿</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L6" s="15" t="n">
+      <c r="L6" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>SRS V1.0 与基线冻结（M1）</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>2027/01/14</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>2027/01/15</t>
         </is>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>AI 成稿</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L7" s="15" t="n">
+      <c r="L7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>架构设计与评审</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>2027/01/06</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr"/>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="inlineStr"/>
+      <c r="J8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>微前端架构设计（Shell/MF/shared/发布）</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>2027/01/06</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>AI 对照案例</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr"/>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L9" s="15" t="n">
+      <c r="L9" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>后端架构设计（服务拆分/APIM/事件/安全）</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>2027/01/06</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>AI 对照案例</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr"/>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L10" s="15" t="n">
+      <c r="L10" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>1.2.3</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>外部架构评审#1 + ADR 定稿（M2 组成）</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>2027/01/22</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>AI 整理评审意见</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>1.2.1,1.2.2</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L11" s="15" t="n">
+      <c r="L11" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>二、平台工程与环境（W1~W4）</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>2027/01/04</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>AKS 三环境 + Terraform IaC</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>2027/01/06</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>2027/01/27</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>AI 生成模块代码</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr"/>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>CI/CD 流水线与质量门禁</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>AI 生成流水线</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L14" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>可观测基线（日志/APM/告警）</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>AI 生成仪表盘</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>三、微前端底座（W2~W6）</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Wade/FE-B</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>2027/01/07</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>2027/02/12</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr">
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Portal Shell 宿主</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>2027/01/07</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>2027/02/05</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L17" s="13" t="n">
+      <c r="L17" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>路由/布局/RBAC 菜单下发</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>2027/01/07</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>AI 生成脚手架</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L18" s="15" t="n">
+      <c r="L18" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>SSO 会话与权限 SDK</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L19" s="15" t="n">
+      <c r="L19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>MF 注册表与运行时加载</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>AI 生成加载器</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L20" s="15" t="n">
+      <c r="L20" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>3.1.4</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Design Tokens/主题/错误兜底/事件总线</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>2027/02/05</t>
         </is>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L21" s="15" t="n">
+      <c r="L21" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>MF 工程化与 shared 治理</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Wade/FE-B</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>2027/02/04</t>
         </is>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="12" t="inlineStr"/>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="inlineStr"/>
+      <c r="J22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>3.2.1</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>模块脚手架模板 + 本地联调</t>
         </is>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>2027/01/25</t>
         </is>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H23" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>AI 生成模板</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K23" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L23" s="15" t="n">
+      <c r="L23" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>shared 白名单与版本协商 + CI 校验</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>FE-B</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>2027/02/04</t>
         </is>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H24" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>3.2.1</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L24" s="15" t="n">
+      <c r="L24" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>组件库基础版</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>FE-B</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>2027/01/15</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>2027/02/12</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="12" t="inlineStr"/>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="inlineStr"/>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L25" s="13" t="n">
+      <c r="L25" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>基础组件（Antd 定制/表单表格）</t>
         </is>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>FE-B</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>2027/01/15</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H26" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>AI 生成组件</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr"/>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L26" s="15" t="n">
+      <c r="L26" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>3.3.2</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>业务组件（内容卡片/审核流/签到）</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>FE-B</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>2027/01/27</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>2027/02/12</t>
         </is>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>AI 生成组件</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="K27" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L27" s="15" t="n">
+      <c r="L27" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>契约包与模块发布机制</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="inlineStr"/>
-      <c r="J28" s="12" t="inlineStr"/>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L28" s="13" t="n">
+      <c r="L28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>3.4.1</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>@abbott/contracts 契约包</t>
         </is>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H29" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>OpenAPI 生成</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K29" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L29" s="15" t="n">
+      <c r="L29" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>3.4.2</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>CDN 发布 + manifest PR + 回滚演练</t>
         </is>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H30" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>AI 脚本</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>3.4.1,2.2</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K30" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L30" s="15" t="n">
+      <c r="L30" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>四、后端通用服务（W3~W9）</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>2027/03/12</t>
         </is>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>服务模板与脚手架</t>
         </is>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C32" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>AI 生成模板</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L32" s="13" t="n">
+      <c r="L32" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>统一身份与 SSO（identity）</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="inlineStr"/>
-      <c r="J33" s="12" t="inlineStr"/>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="14" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>4.2.1</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Entra ID OIDC 对接 + 会话</t>
         </is>
       </c>
-      <c r="C34" s="15" t="n">
+      <c r="C34" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>2027/01/13</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>2027/01/27</t>
         </is>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H34" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K34" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L34" s="15" t="n">
+      <c r="L34" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>4.2.2</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>用户/角色/组织管理 API+界面后端</t>
         </is>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>AI 生成 CRUD</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="K35" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L35" s="15" t="n">
+      <c r="L35" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>4.2.3</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>RBAC+数据范围权限模型</t>
         </is>
       </c>
-      <c r="C36" s="15" t="n">
+      <c r="C36" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>2027/01/25</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>4.2.2</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
+      <c r="K36" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L36" s="15" t="n">
+      <c r="L36" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>事件骨干 + 内部 APIM</t>
         </is>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>2027/02/25</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="inlineStr"/>
-      <c r="J37" s="12" t="inlineStr"/>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L37" s="13" t="n">
+      <c r="L37" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Service Bus 主题/Outbox/幂等/DLQ</t>
         </is>
       </c>
-      <c r="C38" s="15" t="n">
+      <c r="C38" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>2027/01/21</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H38" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
+      <c r="K38" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L38" s="15" t="n">
+      <c r="L38" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>内部 APIM 产品/策略/限流</t>
         </is>
       </c>
-      <c r="C39" s="15" t="n">
+      <c r="C39" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>2027/02/25</t>
         </is>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H39" s="15" t="n">
+      <c r="H39" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>AI 生成策略</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="K39" s="14" t="inlineStr">
+      <c r="K39" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L39" s="15" t="n">
+      <c r="L39" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>通知/工作流/规则/文件/审计</t>
         </is>
       </c>
-      <c r="C40" s="13" t="n">
+      <c r="C40" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>2027/01/27</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>2027/03/12</t>
         </is>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="inlineStr"/>
-      <c r="J40" s="12" t="inlineStr"/>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L40" s="13" t="n">
+      <c r="L40" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>4.4.1</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>通知服务（三渠道+模板）</t>
         </is>
       </c>
-      <c r="C41" s="15" t="n">
+      <c r="C41" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>2027/01/27</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>2027/02/12</t>
         </is>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H41" s="15" t="n">
+      <c r="H41" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr">
+      <c r="K41" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L41" s="15" t="n">
+      <c r="L41" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>工作流引擎（审批流）</t>
         </is>
       </c>
-      <c r="C42" s="15" t="n">
+      <c r="C42" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>2027/03/01</t>
         </is>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="H42" s="15" t="n">
+      <c r="H42" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="K42" s="14" t="inlineStr">
+      <c r="K42" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L42" s="15" t="n">
+      <c r="L42" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>4.4.3</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>规则引擎 + 文件服务 + 审计服务</t>
         </is>
       </c>
-      <c r="C43" s="15" t="n">
+      <c r="C43" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>2027/03/12</t>
         </is>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="H43" s="15" t="n">
+      <c r="H43" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="K43" s="14" t="inlineStr">
+      <c r="K43" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L43" s="15" t="n">
+      <c r="L43" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>五、三域业务交付（W5~W14）</t>
         </is>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>2027/04/13</t>
         </is>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
-      <c r="K44" s="10" t="inlineStr">
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="13" t="inlineStr"/>
+      <c r="J44" s="13" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Content Hub（产品+学术）</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Wade/BE-B</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>2027/03/19</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="H45" s="12" t="n"/>
-      <c r="I45" s="12" t="inlineStr"/>
-      <c r="J45" s="12" t="inlineStr"/>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="inlineStr"/>
+      <c r="J45" s="14" t="inlineStr"/>
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L45" s="13" t="n">
+      <c r="L45" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>产品中心 API（列表/详情/资料/速查）</t>
         </is>
       </c>
-      <c r="C46" s="15" t="n">
+      <c r="C46" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>2027/01/29</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>2027/02/23</t>
         </is>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H46" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>AI 生成 CRUD</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>4.2.3</t>
         </is>
       </c>
-      <c r="K46" s="14" t="inlineStr">
+      <c r="K46" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L46" s="15" t="n">
+      <c r="L46" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>5.1.2</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>学术中心 API（文献/课程/学习记录）</t>
         </is>
       </c>
-      <c r="C47" s="15" t="n">
+      <c r="C47" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>2027/03/05</t>
         </is>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H47" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>AI 生成 CRUD</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="K47" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L47" s="15" t="n">
+      <c r="L47" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>5.1.3</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>内容审核发布流 + 基础搜索</t>
         </is>
       </c>
-      <c r="C48" s="15" t="n">
+      <c r="C48" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>BE-B/DevB</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>2027/02/23</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>2027/03/15</t>
         </is>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H48" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K48" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L48" s="15" t="n">
+      <c r="L48" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>5.1.4</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>Product MF + Content MF 页面</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n">
+      <c r="C49" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>2027/02/08</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>2027/03/19</t>
         </is>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H49" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="I49" s="16" t="inlineStr">
         <is>
           <t>AI 生成页面</t>
         </is>
       </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>3.2.1,5.1.1</t>
         </is>
       </c>
-      <c r="K49" s="14" t="inlineStr">
+      <c r="K49" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L49" s="15" t="n">
+      <c r="L49" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>5.1.5</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>端到端 MVP 打穿（M3）</t>
         </is>
       </c>
-      <c r="C50" s="15" t="n">
+      <c r="C50" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>2027/02/24</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>2027/03/05</t>
         </is>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H50" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>AI 补齐用例</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>5.1.3,5.1.4</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="K50" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L50" s="15" t="n">
+      <c r="L50" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>Event Hub（会议）</t>
         </is>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>FE-B/BE-B</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>2027/02/25</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="14" t="inlineStr">
         <is>
           <t>2027/04/07</t>
         </is>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="H51" s="12" t="n"/>
-      <c r="I51" s="12" t="inlineStr"/>
-      <c r="J51" s="12" t="inlineStr"/>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="H51" s="14" t="n"/>
+      <c r="I51" s="14" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr"/>
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L51" s="13" t="n">
+      <c r="L51" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>5.2.1</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>会议/议程管理 API</t>
         </is>
       </c>
-      <c r="C52" s="15" t="n">
+      <c r="C52" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>2027/02/25</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>2027/03/15</t>
         </is>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I52" s="14" t="inlineStr">
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>AI 生成 CRUD</t>
         </is>
       </c>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="K52" s="14" t="inlineStr">
+      <c r="K52" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L52" s="15" t="n">
+      <c r="L52" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>5.2.2</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>报名审核 + 二维码签到</t>
         </is>
       </c>
-      <c r="C53" s="15" t="n">
+      <c r="C53" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>2027/03/05</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>2027/03/25</t>
         </is>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H53" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I53" s="14" t="inlineStr">
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J53" s="14" t="inlineStr">
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>5.2.1,4.4.2</t>
         </is>
       </c>
-      <c r="K53" s="14" t="inlineStr">
+      <c r="K53" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L53" s="15" t="n">
+      <c r="L53" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>5.2.3</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>第三方直播对接（最简）</t>
         </is>
       </c>
-      <c r="C54" s="15" t="n">
+      <c r="C54" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>2027/03/15</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>2027/03/29</t>
         </is>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H54" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>AI 生成适配器</t>
         </is>
       </c>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="J54" s="16" t="inlineStr">
         <is>
           <t>5.2.1</t>
         </is>
       </c>
-      <c r="K54" s="14" t="inlineStr">
+      <c r="K54" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L54" s="15" t="n">
+      <c r="L54" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>5.2.4</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Event MF 页面</t>
         </is>
       </c>
-      <c r="C55" s="15" t="n">
+      <c r="C55" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>FE-B</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>2027/03/05</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>2027/04/07</t>
         </is>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="H55" s="15" t="n">
+      <c r="H55" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>AI 生成页面</t>
         </is>
       </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="J55" s="16" t="inlineStr">
         <is>
           <t>3.3.2,5.2.1</t>
         </is>
       </c>
-      <c r="K55" s="14" t="inlineStr">
+      <c r="K55" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L55" s="15" t="n">
+      <c r="L55" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>Customer Hub（客户360）</t>
         </is>
       </c>
-      <c r="C56" s="13" t="n">
+      <c r="C56" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>Wade/BE-B</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="14" t="inlineStr">
         <is>
           <t>2027/03/11</t>
         </is>
       </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>2027/04/13</t>
         </is>
       </c>
-      <c r="G56" s="13" t="n">
+      <c r="G56" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="H56" s="12" t="n"/>
-      <c r="I56" s="12" t="inlineStr"/>
-      <c r="J56" s="12" t="inlineStr"/>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="H56" s="14" t="n"/>
+      <c r="I56" s="14" t="inlineStr"/>
+      <c r="J56" s="14" t="inlineStr"/>
+      <c r="K56" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L56" s="13" t="n">
+      <c r="L56" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>5.3.1</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>HCP/HCO 主数据 API（含查重导入）</t>
         </is>
       </c>
-      <c r="C57" s="15" t="n">
+      <c r="C57" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>BE-B</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>2027/03/11</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>2027/03/29</t>
         </is>
       </c>
-      <c r="G57" s="15" t="n">
+      <c r="G57" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H57" s="15" t="n">
+      <c r="H57" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>AI 生成 CRUD</t>
         </is>
       </c>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>4.2.3</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="K57" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L57" s="15" t="n">
+      <c r="L57" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>5.3.2</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>C360 聚合视图 + 规则标签</t>
         </is>
       </c>
-      <c r="C58" s="15" t="n">
+      <c r="C58" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>DevB/BE-B</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>2027/03/19</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>2027/04/07</t>
         </is>
       </c>
-      <c r="G58" s="15" t="n">
+      <c r="G58" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H58" s="15" t="n">
+      <c r="H58" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="I58" s="14" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>AI 生成</t>
         </is>
       </c>
-      <c r="J58" s="14" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>5.3.1</t>
         </is>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="K58" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L58" s="15" t="n">
+      <c r="L58" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>5.3.3</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Customer MF 页面（列表/详情/C360）</t>
         </is>
       </c>
-      <c r="C59" s="15" t="n">
+      <c r="C59" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E59" s="16" t="inlineStr">
         <is>
           <t>2027/03/19</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>2027/04/13</t>
         </is>
       </c>
-      <c r="G59" s="15" t="n">
+      <c r="G59" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="H59" s="15" t="n">
+      <c r="H59" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="I59" s="14" t="inlineStr">
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>AI 生成页面</t>
         </is>
       </c>
-      <c r="J59" s="14" t="inlineStr">
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>5.3.1</t>
         </is>
       </c>
-      <c r="K59" s="14" t="inlineStr">
+      <c r="K59" s="16" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L59" s="15" t="n">
+      <c r="L59" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>集成联调与走查（M4）</t>
         </is>
       </c>
-      <c r="C60" s="13" t="n">
+      <c r="C60" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>Mandy/全员</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>2027/03/31</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>2027/04/13</t>
         </is>
       </c>
-      <c r="G60" s="13" t="n">
+      <c r="G60" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H60" s="13" t="n">
+      <c r="H60" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I60" s="12" t="inlineStr">
+      <c r="I60" s="14" t="inlineStr">
         <is>
           <t>AI 生成用例</t>
         </is>
       </c>
-      <c r="J60" s="12" t="inlineStr">
+      <c r="J60" s="14" t="inlineStr">
         <is>
           <t>5.1,5.2,5.3</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
+      <c r="K60" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L60" s="13" t="n">
+      <c r="L60" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="13" t="inlineStr">
         <is>
           <t>六、非功能与交付（W14~W17）</t>
         </is>
       </c>
-      <c r="C61" s="11" t="n">
+      <c r="C61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>2027/04/07</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>2027/05/03</t>
         </is>
       </c>
-      <c r="G61" s="11" t="n">
+      <c r="G61" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr">
+      <c r="H61" s="13" t="n"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr"/>
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L61" s="11" t="n">
+      <c r="L61" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>性能压测与优化</t>
         </is>
       </c>
-      <c r="C62" s="13" t="n">
+      <c r="C62" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>DevB/Wade</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>2027/04/02</t>
         </is>
       </c>
-      <c r="F62" s="12" t="inlineStr">
+      <c r="F62" s="14" t="inlineStr">
         <is>
           <t>2027/04/19</t>
         </is>
       </c>
-      <c r="G62" s="13" t="n">
+      <c r="G62" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="H62" s="13" t="n">
+      <c r="H62" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I62" s="12" t="inlineStr">
+      <c r="I62" s="14" t="inlineStr">
         <is>
           <t>AI 分析报告</t>
         </is>
       </c>
-      <c r="J62" s="12" t="inlineStr">
+      <c r="J62" s="14" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="K62" s="12" t="inlineStr">
+      <c r="K62" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L62" s="13" t="n">
+      <c r="L62" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>安全收口（扫描清零/权限用例）</t>
         </is>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
         <is>
           <t>2027/04/02</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>2027/04/19</t>
         </is>
       </c>
-      <c r="G63" s="13" t="n">
+      <c r="G63" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="H63" s="13" t="n">
+      <c r="H63" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I63" s="12" t="inlineStr">
+      <c r="I63" s="14" t="inlineStr">
         <is>
           <t>AI 扫描</t>
         </is>
       </c>
-      <c r="J63" s="12" t="inlineStr">
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="K63" s="12" t="inlineStr">
+      <c r="K63" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L63" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>UAT 组织与缺陷修复（M5）</t>
         </is>
       </c>
-      <c r="C64" s="13" t="n">
+      <c r="C64" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>Mandy/全员</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
         <is>
           <t>2027/04/09</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>2027/04/21</t>
         </is>
       </c>
-      <c r="G64" s="13" t="n">
+      <c r="G64" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H64" s="13" t="n">
+      <c r="H64" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="12" t="inlineStr">
+      <c r="I64" s="14" t="inlineStr">
         <is>
           <t>AI 生成 UAT 脚本</t>
         </is>
       </c>
-      <c r="J64" s="12" t="inlineStr">
+      <c r="J64" s="14" t="inlineStr">
         <is>
           <t>6.1,6.2</t>
         </is>
       </c>
-      <c r="K64" s="12" t="inlineStr">
+      <c r="K64" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L64" s="13" t="n">
+      <c r="L64" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>文档定稿与运维交接</t>
         </is>
       </c>
-      <c r="C65" s="13" t="n">
+      <c r="C65" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>2027/04/15</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>2027/04/27</t>
         </is>
       </c>
-      <c r="G65" s="13" t="n">
+      <c r="G65" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="H65" s="13" t="n">
+      <c r="H65" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I65" s="12" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>AI 成稿</t>
         </is>
       </c>
-      <c r="J65" s="12" t="inlineStr">
+      <c r="J65" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="K65" s="12" t="inlineStr">
+      <c r="K65" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L65" s="13" t="n">
+      <c r="L65" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>上线预演 + 生产上线（M6）</t>
         </is>
       </c>
-      <c r="C66" s="13" t="n">
+      <c r="C66" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="14" t="inlineStr">
         <is>
           <t>2027/04/26</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="F66" s="14" t="inlineStr">
         <is>
           <t>2027/04/30</t>
         </is>
       </c>
-      <c r="G66" s="13" t="n">
+      <c r="G66" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H66" s="13" t="n">
+      <c r="H66" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I66" s="12" t="inlineStr">
+      <c r="I66" s="14" t="inlineStr">
         <is>
           <t>AI 检查清单</t>
         </is>
       </c>
-      <c r="J66" s="12" t="inlineStr">
+      <c r="J66" s="14" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
+      <c r="K66" s="14" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="L66" s="13" t="n">
+      <c r="L66" s="15" t="n">
         <v>0</v>
       </c>
     </row>
